--- a/multiSchoolOutput/05_Edinburgh_Futures_Institute/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/05_Edinburgh_Futures_Institute/solution_weeks_9_10.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0335_03_3.3</t>
+          <t>0227_01_1.02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1572,7 +1572,7 @@
         <v>30</v>
       </c>
       <c r="F20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0227_01_1.02</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0113_01_1.9</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0227_01_1.02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0201_02_2.12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2516,7 +2516,7 @@
         <v>50</v>
       </c>
       <c r="F36" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2575,7 +2575,7 @@
         <v>300</v>
       </c>
       <c r="F37" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2619,12 +2619,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0110_02_2.04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2636,7 +2636,7 @@
         <v>40</v>
       </c>
       <c r="F38" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0228_11_11.18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0335_04_4.2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2811,7 +2811,7 @@
         <v>30</v>
       </c>
       <c r="F41" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0110_02_2.04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2870,7 +2870,7 @@
         <v>40</v>
       </c>
       <c r="F42" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2988,7 +2988,7 @@
         <v>30</v>
       </c>
       <c r="F44" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3030,12 +3030,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0335_03_3.3</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3224,7 +3224,7 @@
         <v>30</v>
       </c>
       <c r="F48" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3283,7 +3283,7 @@
         <v>30</v>
       </c>
       <c r="F49" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3325,12 +3325,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3384,12 +3384,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0227_02_2.39</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3401,7 +3401,7 @@
         <v>10</v>
       </c>
       <c r="F51" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3443,12 +3443,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3519,7 +3519,7 @@
         <v>30</v>
       </c>
       <c r="F53" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3561,12 +3561,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0003_00_G.03</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3578,7 +3578,7 @@
         <v>10</v>
       </c>
       <c r="F54" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3620,12 +3620,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3637,7 +3637,7 @@
         <v>30</v>
       </c>
       <c r="F55" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0214_00_G.22</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3696,7 +3696,7 @@
         <v>10</v>
       </c>
       <c r="F56" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3738,12 +3738,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0311_04_4.08</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3932,7 +3932,7 @@
         <v>10</v>
       </c>
       <c r="F60" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0201_02_2.06</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4109,7 +4109,7 @@
         <v>10</v>
       </c>
       <c r="F63" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4168,7 +4168,7 @@
         <v>30</v>
       </c>
       <c r="F64" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4210,12 +4210,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0227_02_2.54</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4286,7 +4286,7 @@
         <v>10</v>
       </c>
       <c r="F66" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4328,12 +4328,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0201_02_2.06</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4345,7 +4345,7 @@
         <v>10</v>
       </c>
       <c r="F67" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0227_02_2.03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4404,7 +4404,7 @@
         <v>10</v>
       </c>
       <c r="F68" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0228_06_6.05</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4463,7 +4463,7 @@
         <v>10</v>
       </c>
       <c r="F69" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0300_00_NG.02</t>
+          <t>0450_03_3.35</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0003_00_G.02</t>
+          <t>0228_06_6.11</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5046,12 +5046,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0450_02_2.63</t>
+          <t>0254_01_1.09</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0201_02_2.12</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5185,7 +5185,7 @@
         <v>50</v>
       </c>
       <c r="F81" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0201_02_2.12</t>
+          <t>0201_02_2.14</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0228_02_2.18</t>
+          <t>0254_01_1.07</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0229_01_1.A</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5429,7 +5429,7 @@
         <v>300</v>
       </c>
       <c r="F85" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5473,12 +5473,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0226_04_4.04</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5490,7 +5490,7 @@
         <v>50</v>
       </c>
       <c r="F86" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5534,12 +5534,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0313_00_G.10</t>
+          <t>0201_03_3.09</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0229_01_1.A</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5612,7 +5612,7 @@
         <v>300</v>
       </c>
       <c r="F88" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0113_01_1.9</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0254_01_1.5A</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0112_-1_B.03</t>
+          <t>0450_01_1.52</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0228_01_1.18</t>
+          <t>0214_00_G.26</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5961,12 +5961,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0450_01_1.40</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6161,7 +6161,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -6205,12 +6205,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0254_01_1.09</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6388,12 +6388,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0254_01_1.06</t>
+          <t>0450_03_3.32</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0254_01_1.07</t>
+          <t>0214_01_1.22</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0201_02_2.14</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6527,7 +6527,7 @@
         <v>50</v>
       </c>
       <c r="F103" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6632,12 +6632,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0335_03_3.3</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6876,12 +6876,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0214_01_1.22</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">

--- a/multiSchoolOutput/05_Edinburgh_Futures_Institute/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/05_Edinburgh_Futures_Institute/solution_weeks_9_10.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0450_03_3.42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wednesday 11:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0008_00_G.267</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0113_01_1.9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0227_01_1.02</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thursday 11:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0113_02_2.65</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0335_01_1.9</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1572,7 +1572,7 @@
         <v>30</v>
       </c>
       <c r="F20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0227_01_1.02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0227_01_1.02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0113_01_1.9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0201_02_2.12</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2516,7 +2516,7 @@
         <v>50</v>
       </c>
       <c r="F36" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0201_01_1.06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Friday 12:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2575,7 +2575,7 @@
         <v>300</v>
       </c>
       <c r="F37" t="n">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2619,12 +2619,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0110_02_2.04</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2636,7 +2636,7 @@
         <v>40</v>
       </c>
       <c r="F38" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0228_11_11.18</t>
+          <t>0208_00_G.8</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2794,12 +2794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0335_04_4.2</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2811,7 +2811,7 @@
         <v>30</v>
       </c>
       <c r="F41" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2853,12 +2853,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0110_02_2.04</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2870,7 +2870,7 @@
         <v>40</v>
       </c>
       <c r="F42" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2912,12 +2912,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0335_00_G.10</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2988,7 +2988,7 @@
         <v>30</v>
       </c>
       <c r="F44" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3030,12 +3030,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0335_00_G.10</t>
+          <t>0008_00_G.267</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3224,7 +3224,7 @@
         <v>30</v>
       </c>
       <c r="F48" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0335_00_G.09</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3283,7 +3283,7 @@
         <v>30</v>
       </c>
       <c r="F49" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3325,12 +3325,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3384,12 +3384,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0227_02_2.39</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3401,7 +3401,7 @@
         <v>10</v>
       </c>
       <c r="F51" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3443,12 +3443,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0335_00_G.09</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3519,7 +3519,7 @@
         <v>30</v>
       </c>
       <c r="F53" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3561,12 +3561,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0003_00_G.03</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3578,7 +3578,7 @@
         <v>10</v>
       </c>
       <c r="F54" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3620,12 +3620,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0335_05_5.2</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3637,7 +3637,7 @@
         <v>30</v>
       </c>
       <c r="F55" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3679,12 +3679,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0214_00_G.22</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3696,7 +3696,7 @@
         <v>10</v>
       </c>
       <c r="F56" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3738,12 +3738,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0311_04_4.08</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3932,7 +3932,7 @@
         <v>10</v>
       </c>
       <c r="F60" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0113_01_1.9</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0201_02_2.06</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4109,7 +4109,7 @@
         <v>10</v>
       </c>
       <c r="F63" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0335_00_G.09</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4168,7 +4168,7 @@
         <v>30</v>
       </c>
       <c r="F64" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4210,12 +4210,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0227_02_2.54</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4286,7 +4286,7 @@
         <v>10</v>
       </c>
       <c r="F66" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4328,12 +4328,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0201_02_2.06</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4345,7 +4345,7 @@
         <v>10</v>
       </c>
       <c r="F67" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4387,12 +4387,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0227_02_2.03</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4404,7 +4404,7 @@
         <v>10</v>
       </c>
       <c r="F68" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4446,12 +4446,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0228_06_6.05</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4463,7 +4463,7 @@
         <v>10</v>
       </c>
       <c r="F69" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4505,12 +4505,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4623,12 +4623,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0450_03_3.35</t>
+          <t>0313_00_G.10</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0214_00_G.26</t>
+          <t>0110_02_2.07</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0228_06_6.11</t>
+          <t>0228_07_7.18</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0113_01_1.9</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5046,12 +5046,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0254_01_1.5A</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0201_02_2.12</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5185,7 +5185,7 @@
         <v>50</v>
       </c>
       <c r="F81" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0201_02_2.14</t>
+          <t>0201_02_2.12</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0254_01_1.07</t>
+          <t>0450_01_1.62</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0229_01_1.A</t>
+          <t>0201_01_1.06</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5429,7 +5429,7 @@
         <v>300</v>
       </c>
       <c r="F85" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5473,12 +5473,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0226_04_4.04</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5490,7 +5490,7 @@
         <v>50</v>
       </c>
       <c r="F86" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5534,12 +5534,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0201_03_3.09</t>
+          <t>0335_02_2.14</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0229_01_1.A</t>
+          <t>0201_01_1.06</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5612,7 +5612,7 @@
         <v>300</v>
       </c>
       <c r="F88" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0113_01_1.9</t>
+          <t>0311_01_1.26</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0214_00_G.26</t>
+          <t>0450_03_3.32</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5961,12 +5961,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0450_01_1.40</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6161,7 +6161,7 @@
         <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -6205,12 +6205,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Thursday 11:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0450_03_3.63</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6388,12 +6388,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0450_03_3.32</t>
+          <t>0283_01_1.01</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0214_01_1.22</t>
+          <t>0112_02_2.11</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0201_02_2.14</t>
+          <t>0113_00_G.03</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6527,7 +6527,7 @@
         <v>50</v>
       </c>
       <c r="F103" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6632,12 +6632,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0113_00_G.199</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0254_01_1.09</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6876,12 +6876,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0228_02_2.18</t>
+          <t>0112_04_4.11</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0450_02_2.63</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
